--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL FREIO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL FREIO - 01_02.xlsx
@@ -482,7 +482,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +507,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +528,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -616,7 +628,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -687,7 +703,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -708,7 +728,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -754,7 +778,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -775,7 +803,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL FREIO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL FREIO - 01_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,11 +508,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -553,11 +528,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -578,11 +548,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -603,11 +568,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -628,11 +588,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -653,11 +608,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -678,11 +628,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -703,11 +648,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -728,11 +668,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -753,11 +688,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -778,11 +708,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -803,11 +728,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -824,11 +744,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -847,11 +762,6 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
     </row>
